--- a/exports/donations.xlsx
+++ b/exports/donations.xlsx
@@ -413,20 +413,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
@@ -504,25 +504,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DON-49336E5C</t>
+          <t>DON-3E6C0534</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5437373</t>
+          <t>121212</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kona Meghana</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anantapur</t>
+          <t>tirupathi</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>12345</v>
+        <v>2700</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -545,200 +545,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>donation_1778950070_Screenshot_88.png</t>
+          <t>donation_1779095630_hero.png.png</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Received</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>16-05-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>DON-894349F8</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>5269852</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Kona Meghana</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>22</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Anantapur</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>9390541258</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>UPI</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>345678907667</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>donation_1778950726_Screenshot_28.png</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>16-05-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DON-C78C9604</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>85222</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Ravi</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>54</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Anantapur</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>9390541258</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>UPI</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>345678907667</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>donation_1778951980_Screenshot_108.png</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>16-05-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DON-9B57A033</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>5437373</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Kona Meghana</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>54</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Anantapur</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>9390541258</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>45000</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>UPI</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>345678907667</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>donation_1778952272_Screenshot_119.png</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>16-05-2026</t>
+          <t>18-05-2026</t>
         </is>
       </c>
     </row>
